--- a/artfynd/A 33421-2021 artfynd.xlsx
+++ b/artfynd/A 33421-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33421-2021 artfynd.xlsx
+++ b/artfynd/A 33421-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -908,6 +908,120 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125528967</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57738</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Brudslöjan, Vemdalsskalet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>447189</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6929370</v>
+      </c>
+      <c r="S4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Per Åsberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Per Åsberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33421-2021 artfynd.xlsx
+++ b/artfynd/A 33421-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -913,12 +913,7 @@
         <v>125528967</v>
       </c>
       <c r="B4" t="n">
-        <v>57738</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57755</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,6 +1016,119 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125767256</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58129</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Brudslöjan, Vemdalsskalet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>447189</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6929370</v>
+      </c>
+      <c r="S5" t="n">
+        <v>100</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Åsberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Åsberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33421-2021 artfynd.xlsx
+++ b/artfynd/A 33421-2021 artfynd.xlsx
@@ -1022,7 +1022,7 @@
         <v>125767256</v>
       </c>
       <c r="B5" t="n">
-        <v>58129</v>
+        <v>58130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33421-2021 artfynd.xlsx
+++ b/artfynd/A 33421-2021 artfynd.xlsx
@@ -913,7 +913,7 @@
         <v>125528967</v>
       </c>
       <c r="B4" t="n">
-        <v>57755</v>
+        <v>57756</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>125767256</v>
       </c>
       <c r="B5" t="n">
-        <v>58130</v>
+        <v>58131</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33421-2021 artfynd.xlsx
+++ b/artfynd/A 33421-2021 artfynd.xlsx
@@ -1022,7 +1022,7 @@
         <v>125767256</v>
       </c>
       <c r="B5" t="n">
-        <v>58131</v>
+        <v>58135</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33421-2021 artfynd.xlsx
+++ b/artfynd/A 33421-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105747113</v>
+        <v>111833710</v>
       </c>
       <c r="B2" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,44 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>5754</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brudslöjan, Hjd</t>
+          <t>Brudslöjan, Brudslöjan, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447238.9321539597</v>
+        <v>447324</v>
       </c>
       <c r="R2" t="n">
-        <v>6929482.638475746</v>
+        <v>6929278</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,22 +741,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-12-26</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-12-26</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,66 +771,76 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Tommy Carlström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Olle Jonsson, Johanna Lindeberg</t>
+          <t>Tommy Carlström, Ingela Carlström, Thomas Samuelsson, Ylva Rinaldo</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111833710</v>
+        <v>125767256</v>
       </c>
       <c r="B3" t="n">
-        <v>88966</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5754</v>
+        <v>103018</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brudslöjan (Brudslöjan), Hjd</t>
+          <t>Brudslöjan, Vemdalsskalet, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447323</v>
+        <v>447189</v>
       </c>
       <c r="R3" t="n">
-        <v>6929279</v>
+        <v>6929370</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,22 +864,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:25</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:25</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,72 +884,70 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tommy Carlström</t>
+          <t>Per Åsberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tommy Carlström, Ingela Carlström, Thomas Samuelsson, Ylva Rinaldo</t>
+          <t>Per Åsberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125528967</v>
+        <v>105747113</v>
       </c>
       <c r="B4" t="n">
-        <v>57756</v>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Brudslöjan, Vemdalsskalet, Hjd</t>
+          <t>Brudslöjan, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447189</v>
+        <v>447239</v>
       </c>
       <c r="R4" t="n">
-        <v>6929370</v>
+        <v>6929482</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,12 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2022-12-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2022-12-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,22 +991,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Per Åsberg</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Per Åsberg</t>
+          <t>Olle Jonsson, Johanna Lindeberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125767256</v>
+        <v>125528967</v>
       </c>
       <c r="B5" t="n">
-        <v>58135</v>
+        <v>58057</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103018</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1053,14 +1037,10 @@
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1129,6 +1109,192 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6848329</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vemdalsskalet, 600 m NV om turistanläggningen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>446418</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6929131</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2013-07-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2013-07-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6849695</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97987</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vemdalsskalet, 600 m NV om turistanläggningen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>446418</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6929131</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2013-07-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2013-07-04</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
